--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486373_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486373_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0251</v>
+        <v>3.6282</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3254</v>
+        <v>1.9901</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6997</v>
+        <v>1.6381</v>
       </c>
       <c r="G2" t="n">
         <v>1.4464</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0531</v>
+        <v>-0.45</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4074</v>
+        <v>-0.7426</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3542</v>
+        <v>0.2926</v>
       </c>
       <c r="V2" t="n">
         <v>1.1093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.227</v>
+        <v>1.7087</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9056</v>
+        <v>2.0174</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6786</v>
+        <v>-0.3087</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1565</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0514</v>
+        <v>0.4302</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5612</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.478</v>
+        <v>0.4164</v>
       </c>
       <c r="E4" t="n">
         <v>0.3724</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1056</v>
+        <v>0.0439</v>
       </c>
       <c r="G4" t="n">
         <v>0.3497</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1283</v>
+        <v>0.0667</v>
       </c>
       <c r="T4" t="n">
         <v>-0.548</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6763</v>
+        <v>0.6147</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5824</v>
+        <v>-0.6671</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2234</v>
+        <v>1.4469</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8058</v>
+        <v>-2.114</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2059</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3341</v>
+        <v>-0.4188</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4194</v>
+        <v>0.1111</v>
       </c>
       <c r="V5" t="n">
         <v>-1.13</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1459</v>
+        <v>-1.7311</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5109</v>
+        <v>-0.4101</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6568</v>
+        <v>-1.321</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4337</v>
+        <v>-1.5278</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0432</v>
+        <v>-1.4752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3905</v>
+        <v>-0.0526</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6121</v>
+        <v>-0.2479</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2806</v>
+        <v>0.0182</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6686</v>
+        <v>-0.2661</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0458</v>
+        <v>-1.2799</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.3238</v>
+        <v>-1.4934</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2781</v>
+        <v>0.2136</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6151</v>
+        <v>-0.2034</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7487</v>
+        <v>-0.1622</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8663999999999999</v>
+        <v>-0.0412</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7504</v>
+        <v>-2.3482</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5219</v>
+        <v>-0.3832</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2286</v>
+        <v>-1.965</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5278</v>
+        <v>-1.4337</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4752</v>
+        <v>-1.0432</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0526</v>
+        <v>-0.3905</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2479</v>
+        <v>0.6121</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0182</v>
+        <v>1.2806</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2661</v>
+        <v>-0.6686</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2799</v>
+        <v>-2.0458</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4934</v>
+        <v>-2.3238</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2136</v>
+        <v>0.2781</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2227</v>
+        <v>0.4128</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.274</v>
+        <v>-0.1454</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0513</v>
+        <v>0.5582</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0676</v>
+        <v>-3.8017</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.9563</v>
+        <v>-3.8446</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1113</v>
+        <v>0.0428</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2058</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4693</v>
+        <v>-0.2034</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3184</v>
+        <v>-0.2067</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1508</v>
+        <v>0.0033</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.745</v>
+        <v>-4.3365</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7561</v>
+        <v>-2.5325</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9889</v>
+        <v>-1.804</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8663</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7912</v>
+        <v>-0.3827</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8784</v>
+        <v>-0.6549</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0872</v>
+        <v>0.2722</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3307</v>
+        <v>-5.0648</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4776</v>
+        <v>-3.3659</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8531</v>
+        <v>-1.6989</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4548</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6133</v>
+        <v>-1.3474</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5612</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9403</v>
+        <v>-0.7862</v>
       </c>
       <c r="V10" t="n">
         <v>1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7821</v>
+        <v>-6.3737</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.3258</v>
+        <v>-7.1023</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5437</v>
+        <v>0.7286</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6782</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8837</v>
+        <v>-0.4753</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2089</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3252</v>
+        <v>0.5101</v>
       </c>
       <c r="V11" t="n">
         <v>2.2599</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1989</v>
+        <v>-7.3029</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0943</v>
+        <v>-6.9826</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1046</v>
+        <v>-0.3203</v>
       </c>
       <c r="G12" t="n">
         <v>0.6038</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.365</v>
+        <v>-0.469</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8784</v>
+        <v>-0.7667</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5135</v>
+        <v>0.2977</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.8729</v>
+        <v>-25.8727</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.7943</v>
+        <v>-18.7944</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.078699999999999</v>
+        <v>-7.0785</v>
       </c>
       <c r="G13" t="n">
         <v>-11.1291</v>
@@ -1468,10 +1468,10 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0404</v>
+        <v>-3.0403</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.864100000000001</v>
+        <v>-5.864200000000001</v>
       </c>
       <c r="U13" t="n">
         <v>2.8239</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.9831</v>
+        <v>10.023</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2799</v>
+        <v>5.3917</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7032</v>
+        <v>4.6314</v>
       </c>
       <c r="G14" t="n">
         <v>3.8301</v>
@@ -1546,13 +1546,13 @@
         <v>4.3501</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5429</v>
+        <v>0.5828</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8183</v>
+        <v>-0.7066</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3613</v>
+        <v>1.2894</v>
       </c>
       <c r="V14" t="n">
         <v>1.695</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7328</v>
+        <v>5.1868</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7222</v>
+        <v>-0.6577</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0106</v>
+        <v>5.8445</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8608</v>
+        <v>-0.8369</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9947</v>
+        <v>-0.9094</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8662</v>
+        <v>0.0725</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7581</v>
+        <v>-1.3228</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6816</v>
+        <v>-0.5411</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0765</v>
+        <v>-0.7817</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1028</v>
+        <v>0.4859</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3131</v>
+        <v>-0.3683</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7897</v>
+        <v>0.8542</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>3.9151</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>4.3501</v>
       </c>
       <c r="S15" t="n">
-        <v>1.872</v>
+        <v>0.4137</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1392</v>
+        <v>-0.5948</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7328</v>
+        <v>1.0085</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.352</v>
+        <v>4.7399</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8812</v>
+        <v>0.4929</v>
       </c>
       <c r="F16" t="n">
-        <v>5.2332</v>
+        <v>4.247</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8369</v>
+        <v>1.8608</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9094</v>
+        <v>0.9947</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0725</v>
+        <v>0.8662</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3228</v>
+        <v>0.7581</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5411</v>
+        <v>0.6816</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7817</v>
+        <v>0.0765</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4859</v>
+        <v>1.1028</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3683</v>
+        <v>0.3131</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8542</v>
+        <v>0.7897</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9151</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>4.3501</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4212</v>
+        <v>0.879</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8183</v>
+        <v>-0.0901</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3972</v>
+        <v>0.9692</v>
       </c>
       <c r="V16" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5325</v>
+        <v>3.7469</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9488</v>
+        <v>1.6135</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5837</v>
+        <v>2.1334</v>
       </c>
       <c r="G17" t="n">
         <v>1.8355</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9797</v>
+        <v>1.1942</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8172</v>
+        <v>0.4819</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1626</v>
+        <v>0.7123</v>
       </c>
       <c r="V17" t="n">
         <v>0.9347</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1425</v>
+        <v>3.3738</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1399</v>
+        <v>2.5869</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0026</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>3.0803</v>
@@ -1858,13 +1858,13 @@
         <v>2.6101</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1559</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7346</v>
+        <v>0.5188</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3045</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7708</v>
+        <v>2.8596</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0973</v>
+        <v>-1.2656</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3265</v>
+        <v>4.1252</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5061</v>
+        <v>1.1175</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5261</v>
+        <v>1.3533</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0199</v>
+        <v>-0.2359</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3709</v>
+        <v>0.7136</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6059</v>
+        <v>1.2076</v>
       </c>
       <c r="L19" t="n">
-        <v>0.765</v>
+        <v>-0.494</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8648</v>
+        <v>0.4038</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0799</v>
+        <v>0.1457</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7849</v>
+        <v>0.2582</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="R19" t="n">
         <v>2.3926</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0243</v>
+        <v>0.8721</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7487</v>
+        <v>-0.4566</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2757</v>
+        <v>1.3288</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4652</v>
+        <v>2.3353</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8244</v>
+        <v>2.5385</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2895</v>
+        <v>-0.2032</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1175</v>
+        <v>0.5061</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3533</v>
+        <v>0.5261</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2359</v>
+        <v>-0.0199</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7136</v>
+        <v>2.3709</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2076</v>
+        <v>1.6059</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.494</v>
+        <v>0.765</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4038</v>
+        <v>-1.8648</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1457</v>
+        <v>-1.0799</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2582</v>
+        <v>-0.7849</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
         <v>2.3926</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4777</v>
+        <v>0.5888</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0154</v>
+        <v>0.1899</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4931</v>
+        <v>0.399</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1629</v>
+        <v>-0.0224</v>
       </c>
       <c r="E21" t="n">
-        <v>0.58</v>
+        <v>1.1317</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7429</v>
+        <v>-1.1541</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7975</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0365</v>
+        <v>0.6601</v>
       </c>
       <c r="I21" t="n">
-        <v>0.761</v>
+        <v>0.0319</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6485</v>
+        <v>1.9065</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0365</v>
+        <v>1.0251</v>
       </c>
       <c r="L21" t="n">
-        <v>0.612</v>
+        <v>0.8813</v>
       </c>
       <c r="M21" t="n">
-        <v>0.149</v>
+        <v>-1.2144</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.365</v>
       </c>
       <c r="O21" t="n">
-        <v>0.149</v>
+        <v>-0.8495</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0479</v>
+        <v>-0.0847</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1875</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0205</v>
+        <v>0.1027</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.13</v>
+        <v>-1.4997</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X21" t="n">
         <v>-1.13</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3076</v>
+        <v>-0.1321</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9082</v>
+        <v>0.58</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2158</v>
+        <v>-0.7121</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.7975</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6601</v>
+        <v>0.0365</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0319</v>
+        <v>0.761</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9065</v>
+        <v>0.6485</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0251</v>
+        <v>0.0365</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8813</v>
+        <v>0.612</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2144</v>
+        <v>0.149</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.365</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8495</v>
+        <v>0.149</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3699</v>
+        <v>-0.0171</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.411</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0411</v>
+        <v>0.0514</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4997</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2005</v>
+        <v>-1.8395</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1494</v>
+        <v>-2.8142</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9489</v>
+        <v>0.9747</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3308</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3922</v>
+        <v>-0.0312</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8904</v>
+        <v>-0.5552</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4982</v>
+        <v>0.5239</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.435</v>
+        <v>-2.9084</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7428</v>
+        <v>-2.5193</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6922</v>
+        <v>-0.3891</v>
       </c>
       <c r="G24" t="n">
         <v>0.5769</v>
@@ -2326,13 +2326,13 @@
         <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4693</v>
+        <v>0.0574</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1472</v>
+        <v>0.4503</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4552</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>25.8729</v>
+        <v>27.36289999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>7.078499999999999</v>
+        <v>7.078400000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>18.7943</v>
+        <v>20.2845</v>
       </c>
       <c r="G25" t="n">
         <v>11.129</v>
@@ -2404,19 +2404,19 @@
         <v>23.9257</v>
       </c>
       <c r="S25" t="n">
-        <v>3.0402</v>
+        <v>4.5304</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.8237</v>
+        <v>-2.8238</v>
       </c>
       <c r="U25" t="n">
-        <v>5.8643</v>
+        <v>7.3543</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.434399999999999</v>
+        <v>-2.4344</v>
       </c>
       <c r="W25" t="n">
-        <v>5.496100000000001</v>
+        <v>5.4961</v>
       </c>
       <c r="X25" t="n">
         <v>-7.930599999999998</v>
